--- a/UCC_Report.xlsx
+++ b/UCC_Report.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Telecom_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinesh Thirumal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0C6048-788C-4E2E-AF5C-89B80C191A9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E1C3A8-2F65-45DA-BABC-F96C6B7D56D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{E76070D2-90A0-4A37-A971-D8B772920E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$25</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
   <si>
     <t>DID numbers</t>
   </si>
@@ -78,43 +81,37 @@
     <t>Shree Balaji associate</t>
   </si>
   <si>
-    <t>9347284105</t>
-  </si>
-  <si>
-    <t>9849105810</t>
-  </si>
-  <si>
     <t>Cryptomonk</t>
   </si>
   <si>
+    <t>Nextgen services</t>
+  </si>
+  <si>
+    <t>PursuitCX</t>
+  </si>
+  <si>
+    <t>9990930001</t>
+  </si>
+  <si>
+    <t>salary on time</t>
+  </si>
+  <si>
+    <t>9900839325</t>
+  </si>
+  <si>
+    <t>Stefto</t>
+  </si>
+  <si>
+    <t>8860812829</t>
+  </si>
+  <si>
     <t>DigiCredit</t>
   </si>
   <si>
-    <t>Nextgen services</t>
-  </si>
-  <si>
     <t>Nextgen Services</t>
   </si>
   <si>
-    <t>PursuitCX</t>
-  </si>
-  <si>
-    <t>9990930001</t>
-  </si>
-  <si>
-    <t>salary on time</t>
-  </si>
-  <si>
-    <t>9900839325</t>
-  </si>
-  <si>
-    <t>Stefto</t>
-  </si>
-  <si>
     <t>stefto</t>
-  </si>
-  <si>
-    <t>8860812829</t>
   </si>
 </sst>
 </file>
@@ -559,13 +556,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BBAE93-43D1-46F0-9E47-865BBF288536}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.7265625" style="8"/>
   </cols>
@@ -591,278 +588,278 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+      <c r="A2" s="9">
+        <v>8645426989</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>8645426990</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>8913117722</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9118409892</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>8645426215</v>
+      </c>
+      <c r="B5" s="3">
+        <v>9735816783</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <v>8645426217</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>8645426915</v>
+      </c>
+      <c r="B7" s="3">
+        <v>8978853974</v>
+      </c>
+      <c r="C7" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>8645426917</v>
+      </c>
+      <c r="B8" s="3">
+        <v>8978853974</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>8645426913</v>
+      </c>
+      <c r="B9" s="3">
+        <v>8978853974</v>
+      </c>
+      <c r="C9" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="15">
         <v>8213847366</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B10" s="12">
         <v>8247478886</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C10" s="13">
         <v>46236</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>8213847374</v>
-      </c>
-      <c r="B3" s="12">
-        <v>9347284105</v>
-      </c>
-      <c r="C3" s="13">
-        <v>46233.268055555556</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
-        <v>8213847370</v>
-      </c>
-      <c r="B4" s="12">
-        <v>9700112848</v>
-      </c>
-      <c r="C4" s="13">
-        <v>46232.488194444442</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
-        <v>8213847373</v>
-      </c>
-      <c r="B5" s="12">
-        <v>9849105810</v>
-      </c>
-      <c r="C5" s="13">
-        <v>46232.392361111109</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
-        <v>8213846422</v>
-      </c>
-      <c r="B6" s="12">
-        <v>9884892126</v>
-      </c>
-      <c r="C6" s="13">
-        <v>46227.490972222222</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
-        <v>8213847373</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="15">
+        <v>8213846319</v>
+      </c>
+      <c r="B11" s="15">
+        <v>8074615582</v>
+      </c>
+      <c r="C11" s="16">
+        <v>46225.469444444447</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13">
-        <v>46233.270833333336</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
-        <v>8213847372</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="13">
-        <v>46232.397222222222</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
-        <v>8213846319</v>
-      </c>
-      <c r="B9" s="15">
-        <v>8074615582</v>
-      </c>
-      <c r="C9" s="16">
-        <v>46225.469444444447</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="15">
+        <v>8213827736</v>
+      </c>
+      <c r="B12" s="15">
+        <v>9939363385</v>
+      </c>
+      <c r="C12" s="16">
+        <v>46224.552777777775</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="15">
+        <v>8213847240</v>
+      </c>
+      <c r="B13" s="15">
+        <v>7988340945</v>
+      </c>
+      <c r="C13" s="16">
+        <v>46226.493055555555</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
-        <v>8645426989</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="9">
-        <v>8645426990</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>8917116999</v>
-      </c>
-      <c r="B12" s="1">
-        <v>9538043938</v>
-      </c>
-      <c r="C12" s="5">
-        <v>46236</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="15">
+        <v>8213847240</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
-        <v>8917116999</v>
-      </c>
-      <c r="B13" s="12">
-        <v>9913748143</v>
-      </c>
-      <c r="C13" s="13">
-        <v>46211</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>8913117722</v>
-      </c>
-      <c r="B14" s="3">
-        <v>9118409892</v>
-      </c>
-      <c r="C14" s="4">
-        <v>46231</v>
+      <c r="C14" s="16">
+        <v>46226.497916666667</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="12">
+        <v>8213846807</v>
+      </c>
+      <c r="B15" s="12">
+        <v>9966102667</v>
+      </c>
+      <c r="C15" s="13">
+        <v>46219.770833333336</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="15">
-        <v>8213827736</v>
-      </c>
-      <c r="B15" s="15">
-        <v>9939363385</v>
-      </c>
-      <c r="C15" s="16">
-        <v>46224.552777777775</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
       </c>
@@ -871,57 +868,57 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="12">
-        <v>8917103547</v>
-      </c>
-      <c r="B16" s="12">
-        <v>9101317056</v>
-      </c>
-      <c r="C16" s="13">
-        <v>46208</v>
+      <c r="A16" s="15">
+        <v>8213847464</v>
+      </c>
+      <c r="B16" s="15">
+        <v>7993637639</v>
+      </c>
+      <c r="C16" s="16">
+        <v>46226.930555555555</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F16" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
-        <v>8917103701</v>
+      <c r="A17" s="15">
+        <v>8213847463</v>
       </c>
       <c r="B17" s="12">
-        <v>9267902034</v>
+        <v>9900839325</v>
       </c>
       <c r="C17" s="13">
-        <v>46221</v>
+        <v>46234.477777777778</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F17" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
-        <v>8213847240</v>
-      </c>
-      <c r="B18" s="15">
-        <v>7988340945</v>
-      </c>
-      <c r="C18" s="16">
-        <v>46226.493055555555</v>
+        <v>8213847463</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="13">
+        <v>46234.521527777775</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>13</v>
@@ -932,13 +929,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
-        <v>8213847240</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="16">
-        <v>46226.497916666667</v>
+        <v>8213847131</v>
+      </c>
+      <c r="B19" s="12">
+        <v>8860812829</v>
+      </c>
+      <c r="C19" s="13">
+        <v>46234.29791666667</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>23</v>
@@ -951,243 +948,123 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
-        <v>8213846807</v>
+      <c r="A20" s="15">
+        <v>8213846728</v>
       </c>
       <c r="B20" s="12">
-        <v>9966102667</v>
+        <v>9771436278</v>
       </c>
       <c r="C20" s="13">
-        <v>46219.770833333336</v>
+        <v>46234.495833333334</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="15">
+        <v>8213847131</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="13">
+        <v>46235.183333333334</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>8917116999</v>
+      </c>
+      <c r="B22" s="1">
+        <v>9538043938</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46236</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
-        <v>8645426215</v>
-      </c>
-      <c r="B21" s="3">
-        <v>9735816783</v>
-      </c>
-      <c r="C21" s="4">
-        <v>46231</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="9">
-        <v>8645426217</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>16</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
-        <v>8645426915</v>
-      </c>
-      <c r="B23" s="3">
-        <v>8978853974</v>
-      </c>
-      <c r="C23" s="4">
-        <v>46231</v>
+      <c r="A23" s="12">
+        <v>8917116999</v>
+      </c>
+      <c r="B23" s="12">
+        <v>9913748143</v>
+      </c>
+      <c r="C23" s="13">
+        <v>46211</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
-        <v>8645426917</v>
-      </c>
-      <c r="B24" s="3">
-        <v>8978853974</v>
-      </c>
-      <c r="C24" s="4">
-        <v>46231</v>
+      <c r="A24" s="12">
+        <v>8917103547</v>
+      </c>
+      <c r="B24" s="12">
+        <v>9101317056</v>
+      </c>
+      <c r="C24" s="13">
+        <v>46208</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>8645426913</v>
-      </c>
-      <c r="B25" s="3">
-        <v>8978853974</v>
-      </c>
-      <c r="C25" s="4">
-        <v>46231</v>
+      <c r="A25" s="12">
+        <v>8917103701</v>
+      </c>
+      <c r="B25" s="12">
+        <v>9267902034</v>
+      </c>
+      <c r="C25" s="13">
+        <v>46221</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" s="7">
         <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="15">
-        <v>8213847464</v>
-      </c>
-      <c r="B26" s="15">
-        <v>7993637639</v>
-      </c>
-      <c r="C26" s="16">
-        <v>46226.930555555555</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="15">
-        <v>8213847463</v>
-      </c>
-      <c r="B27" s="12">
-        <v>9900839325</v>
-      </c>
-      <c r="C27" s="13">
-        <v>46234.477777777778</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="15">
-        <v>8213847463</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="13">
-        <v>46234.521527777775</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="15">
-        <v>8213847131</v>
-      </c>
-      <c r="B29" s="12">
-        <v>8860812829</v>
-      </c>
-      <c r="C29" s="13">
-        <v>46234.29791666667</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="15">
-        <v>8213846728</v>
-      </c>
-      <c r="B30" s="12">
-        <v>9771436278</v>
-      </c>
-      <c r="C30" s="13">
-        <v>46234.495833333334</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="15">
-        <v>8213847131</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="13">
-        <v>46235.183333333334</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="7">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/UCC_Report.xlsx
+++ b/UCC_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinesh Thirumal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E1C3A8-2F65-45DA-BABC-F96C6B7D56D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE873F3-B1F1-4213-B970-B33044FBA0D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{E76070D2-90A0-4A37-A971-D8B772920E60}"/>
   </bookViews>
@@ -688,60 +688,60 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>8645426915</v>
-      </c>
-      <c r="B7" s="3">
-        <v>8978853974</v>
-      </c>
-      <c r="C7" s="4">
-        <v>46231</v>
+      <c r="A7" s="15">
+        <v>8213847366</v>
+      </c>
+      <c r="B7" s="12">
+        <v>8247478886</v>
+      </c>
+      <c r="C7" s="13">
+        <v>46236</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F7" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>8645426917</v>
-      </c>
-      <c r="B8" s="3">
-        <v>8978853974</v>
-      </c>
-      <c r="C8" s="4">
-        <v>46231</v>
+      <c r="A8" s="15">
+        <v>8213846319</v>
+      </c>
+      <c r="B8" s="15">
+        <v>8074615582</v>
+      </c>
+      <c r="C8" s="16">
+        <v>46225.469444444447</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F8" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>8645426913</v>
-      </c>
-      <c r="B9" s="3">
-        <v>8978853974</v>
-      </c>
-      <c r="C9" s="4">
-        <v>46231</v>
+      <c r="A9" s="15">
+        <v>8213827736</v>
+      </c>
+      <c r="B9" s="15">
+        <v>9939363385</v>
+      </c>
+      <c r="C9" s="16">
+        <v>46224.552777777775</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F9" s="7">
         <v>3</v>
@@ -749,16 +749,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="15">
-        <v>8213847366</v>
-      </c>
-      <c r="B10" s="12">
-        <v>8247478886</v>
-      </c>
-      <c r="C10" s="13">
-        <v>46236</v>
+        <v>8213847240</v>
+      </c>
+      <c r="B10" s="15">
+        <v>7988340945</v>
+      </c>
+      <c r="C10" s="16">
+        <v>46226.493055555555</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
@@ -769,16 +769,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="15">
-        <v>8213846319</v>
-      </c>
-      <c r="B11" s="15">
-        <v>8074615582</v>
+        <v>8213847240</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="C11" s="16">
-        <v>46225.469444444447</v>
+        <v>46226.497916666667</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
@@ -788,17 +788,17 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
-        <v>8213827736</v>
-      </c>
-      <c r="B12" s="15">
-        <v>9939363385</v>
-      </c>
-      <c r="C12" s="16">
-        <v>46224.552777777775</v>
+      <c r="A12" s="12">
+        <v>8213846807</v>
+      </c>
+      <c r="B12" s="12">
+        <v>9966102667</v>
+      </c>
+      <c r="C12" s="13">
+        <v>46219.770833333336</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>13</v>
@@ -809,16 +809,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="15">
-        <v>8213847240</v>
+        <v>8213847464</v>
       </c>
       <c r="B13" s="15">
-        <v>7988340945</v>
+        <v>7993637639</v>
       </c>
       <c r="C13" s="16">
-        <v>46226.493055555555</v>
+        <v>46226.930555555555</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>13</v>
@@ -829,16 +829,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="15">
-        <v>8213847240</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="16">
-        <v>46226.497916666667</v>
+        <v>8213847463</v>
+      </c>
+      <c r="B14" s="12">
+        <v>9900839325</v>
+      </c>
+      <c r="C14" s="13">
+        <v>46234.477777777778</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>13</v>
@@ -848,17 +848,17 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
-        <v>8213846807</v>
-      </c>
-      <c r="B15" s="12">
-        <v>9966102667</v>
+      <c r="A15" s="15">
+        <v>8213847463</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="C15" s="13">
-        <v>46219.770833333336</v>
+        <v>46234.521527777775</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -869,16 +869,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="15">
-        <v>8213847464</v>
-      </c>
-      <c r="B16" s="15">
-        <v>7993637639</v>
-      </c>
-      <c r="C16" s="16">
-        <v>46226.930555555555</v>
+        <v>8213847131</v>
+      </c>
+      <c r="B16" s="12">
+        <v>8860812829</v>
+      </c>
+      <c r="C16" s="13">
+        <v>46234.29791666667</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>13</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="15">
-        <v>8213847463</v>
+        <v>8213846728</v>
       </c>
       <c r="B17" s="12">
-        <v>9900839325</v>
+        <v>9771436278</v>
       </c>
       <c r="C17" s="13">
-        <v>46234.477777777778</v>
+        <v>46234.495833333334</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>13</v>
@@ -909,16 +909,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
-        <v>8213847463</v>
+        <v>8213847131</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="13">
-        <v>46234.521527777775</v>
+        <v>46235.183333333334</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>13</v>
@@ -928,77 +928,77 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="15">
-        <v>8213847131</v>
-      </c>
-      <c r="B19" s="12">
-        <v>8860812829</v>
-      </c>
-      <c r="C19" s="13">
-        <v>46234.29791666667</v>
+      <c r="A19" s="1">
+        <v>8917116999</v>
+      </c>
+      <c r="B19" s="1">
+        <v>9538043938</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46236</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="15">
-        <v>8213846728</v>
+      <c r="A20" s="12">
+        <v>8917116999</v>
       </c>
       <c r="B20" s="12">
-        <v>9771436278</v>
+        <v>9913748143</v>
       </c>
       <c r="C20" s="13">
-        <v>46234.495833333334</v>
+        <v>46211</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F20" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="15">
-        <v>8213847131</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>24</v>
+      <c r="A21" s="12">
+        <v>8917103547</v>
+      </c>
+      <c r="B21" s="12">
+        <v>9101317056</v>
       </c>
       <c r="C21" s="13">
-        <v>46235.183333333334</v>
+        <v>46208</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F21" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>8917116999</v>
-      </c>
-      <c r="B22" s="1">
-        <v>9538043938</v>
-      </c>
-      <c r="C22" s="5">
-        <v>46236</v>
+      <c r="A22" s="12">
+        <v>8917103701</v>
+      </c>
+      <c r="B22" s="12">
+        <v>9267902034</v>
+      </c>
+      <c r="C22" s="13">
+        <v>46221</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>

--- a/UCC_Report.xlsx
+++ b/UCC_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinesh Thirumal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE873F3-B1F1-4213-B970-B33044FBA0D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3220F5-F6BA-4A4B-93D9-585E8474083E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{E76070D2-90A0-4A37-A971-D8B772920E60}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>DID numbers</t>
   </si>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BBAE93-43D1-46F0-9E47-865BBF288536}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
@@ -704,7 +704,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -724,7 +724,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -744,7 +744,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1004,66 +1004,6 @@
         <v>7</v>
       </c>
       <c r="F22" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
-        <v>8917116999</v>
-      </c>
-      <c r="B23" s="12">
-        <v>9913748143</v>
-      </c>
-      <c r="C23" s="13">
-        <v>46211</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="12">
-        <v>8917103547</v>
-      </c>
-      <c r="B24" s="12">
-        <v>9101317056</v>
-      </c>
-      <c r="C24" s="13">
-        <v>46208</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="12">
-        <v>8917103701</v>
-      </c>
-      <c r="B25" s="12">
-        <v>9267902034</v>
-      </c>
-      <c r="C25" s="13">
-        <v>46221</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="7">
         <v>3</v>
       </c>
     </row>

--- a/UCC_Report.xlsx
+++ b/UCC_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinesh Thirumal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3220F5-F6BA-4A4B-93D9-585E8474083E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A7E981-3D5B-48A9-B0D1-B985D35E4D31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{E76070D2-90A0-4A37-A971-D8B772920E60}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>DID numbers</t>
   </si>
@@ -51,18 +51,12 @@
     <t>SKA</t>
   </si>
   <si>
-    <t>Vi</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
     <t>Digicredit</t>
   </si>
   <si>
-    <t>Allset</t>
-  </si>
-  <si>
     <t>9984125538</t>
   </si>
   <si>
@@ -90,28 +84,28 @@
     <t>PursuitCX</t>
   </si>
   <si>
-    <t>9990930001</t>
-  </si>
-  <si>
     <t>salary on time</t>
   </si>
   <si>
-    <t>9900839325</t>
-  </si>
-  <si>
     <t>Stefto</t>
   </si>
   <si>
     <t>8860812829</t>
   </si>
   <si>
-    <t>DigiCredit</t>
-  </si>
-  <si>
-    <t>Nextgen Services</t>
-  </si>
-  <si>
     <t>stefto</t>
+  </si>
+  <si>
+    <t>Mahavir</t>
+  </si>
+  <si>
+    <t>7905301218</t>
+  </si>
+  <si>
+    <t>Strideone</t>
+  </si>
+  <si>
+    <t>VGM</t>
   </si>
 </sst>
 </file>
@@ -192,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -206,9 +200,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -227,20 +218,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,446 +549,446 @@
     <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="8"/>
+    <col min="6" max="6" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>8213846319</v>
+      </c>
+      <c r="B2" s="1">
+        <v>8074615582</v>
+      </c>
+      <c r="C2" s="12">
+        <v>46225.469444444447</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>8213847431</v>
+      </c>
+      <c r="B3" s="1">
+        <v>9676654721</v>
+      </c>
+      <c r="C3" s="13">
+        <v>46237.211111111108</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>8213847518</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9527314872</v>
+      </c>
+      <c r="C4" s="13">
+        <v>46237.304166666669</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>8213827736</v>
+      </c>
+      <c r="B5" s="1">
+        <v>9939363385</v>
+      </c>
+      <c r="C5" s="12">
+        <v>46224.552777777775</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>8213847240</v>
+      </c>
+      <c r="B6" s="1">
+        <v>7988340945</v>
+      </c>
+      <c r="C6" s="12">
+        <v>46226.493055555555</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>8213847240</v>
+      </c>
+      <c r="B7" s="1">
+        <v>9990930001</v>
+      </c>
+      <c r="C7" s="12">
+        <v>46226.497916666667</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>8213846807</v>
+      </c>
+      <c r="B8" s="1">
+        <v>9966102667</v>
+      </c>
+      <c r="C8" s="13">
+        <v>46219.770833333336</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8213847464</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7993637639</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46226.930555555555</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>8213847426</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9686505209</v>
+      </c>
+      <c r="C10" s="13">
+        <v>46237.184027777781</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>8213846738</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7905301218</v>
+      </c>
+      <c r="C11" s="13">
+        <v>46238.200694444444</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>8213847131</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8860812829</v>
+      </c>
+      <c r="C12" s="13">
+        <v>46234.29791666667</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>8213846728</v>
+      </c>
+      <c r="B13" s="1">
+        <v>9771436278</v>
+      </c>
+      <c r="C13" s="13">
+        <v>46234.495833333334</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>8213846727</v>
+      </c>
+      <c r="B14" s="1">
+        <v>9952466520</v>
+      </c>
+      <c r="C14" s="13">
+        <v>46236.770833333336</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>8213846736</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="13">
+        <v>46235.3125</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>8213847131</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="13">
+        <v>46235.183333333334</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>8213842180</v>
+      </c>
+      <c r="B17" s="1">
+        <v>9995866686</v>
+      </c>
+      <c r="C17" s="13">
+        <v>46234.201388888891</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>8645426989</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>8645426990</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
-        <v>8645426989</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="E19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>8913117722</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9118409892</v>
+      </c>
+      <c r="C20" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>8645426215</v>
+      </c>
+      <c r="B21" s="3">
+        <v>9735816783</v>
+      </c>
+      <c r="C21" s="4">
+        <v>46231</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>8645426217</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
-        <v>8645426990</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>8913117722</v>
-      </c>
-      <c r="B4" s="3">
-        <v>9118409892</v>
-      </c>
-      <c r="C4" s="4">
-        <v>46231</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>8645426215</v>
-      </c>
-      <c r="B5" s="3">
-        <v>9735816783</v>
-      </c>
-      <c r="C5" s="4">
-        <v>46231</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <v>8645426217</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
-        <v>8213847366</v>
-      </c>
-      <c r="B7" s="12">
-        <v>8247478886</v>
-      </c>
-      <c r="C7" s="13">
-        <v>46236</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
-        <v>8213846319</v>
-      </c>
-      <c r="B8" s="15">
-        <v>8074615582</v>
-      </c>
-      <c r="C8" s="16">
-        <v>46225.469444444447</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
-        <v>8213827736</v>
-      </c>
-      <c r="B9" s="15">
-        <v>9939363385</v>
-      </c>
-      <c r="C9" s="16">
-        <v>46224.552777777775</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
-        <v>8213847240</v>
-      </c>
-      <c r="B10" s="15">
-        <v>7988340945</v>
-      </c>
-      <c r="C10" s="16">
-        <v>46226.493055555555</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
-        <v>8213847240</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="16">
-        <v>46226.497916666667</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="12">
-        <v>8213846807</v>
-      </c>
-      <c r="B12" s="12">
-        <v>9966102667</v>
-      </c>
-      <c r="C12" s="13">
-        <v>46219.770833333336</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="15">
-        <v>8213847464</v>
-      </c>
-      <c r="B13" s="15">
-        <v>7993637639</v>
-      </c>
-      <c r="C13" s="16">
-        <v>46226.930555555555</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="15">
-        <v>8213847463</v>
-      </c>
-      <c r="B14" s="12">
-        <v>9900839325</v>
-      </c>
-      <c r="C14" s="13">
-        <v>46234.477777777778</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="15">
-        <v>8213847463</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13">
-        <v>46234.521527777775</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="15">
-        <v>8213847131</v>
-      </c>
-      <c r="B16" s="12">
-        <v>8860812829</v>
-      </c>
-      <c r="C16" s="13">
-        <v>46234.29791666667</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="15">
-        <v>8213846728</v>
-      </c>
-      <c r="B17" s="12">
-        <v>9771436278</v>
-      </c>
-      <c r="C17" s="13">
-        <v>46234.495833333334</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="15">
-        <v>8213847131</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="13">
-        <v>46235.183333333334</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>8917116999</v>
-      </c>
-      <c r="B19" s="1">
-        <v>9538043938</v>
-      </c>
-      <c r="C19" s="5">
-        <v>46236</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
-        <v>8917116999</v>
-      </c>
-      <c r="B20" s="12">
-        <v>9913748143</v>
-      </c>
-      <c r="C20" s="13">
-        <v>46211</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="12">
-        <v>8917103547</v>
-      </c>
-      <c r="B21" s="12">
-        <v>9101317056</v>
-      </c>
-      <c r="C21" s="13">
-        <v>46208</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
-        <v>8917103701</v>
-      </c>
-      <c r="B22" s="12">
-        <v>9267902034</v>
-      </c>
-      <c r="C22" s="13">
-        <v>46221</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>3</v>
       </c>
     </row>

--- a/UCC_Report.xlsx
+++ b/UCC_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinesh Thirumal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A7E981-3D5B-48A9-B0D1-B985D35E4D31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58705AF6-B407-4040-BCB9-4A932B62FF6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{E76070D2-90A0-4A37-A971-D8B772920E60}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>DID numbers</t>
   </si>
@@ -45,9 +45,6 @@
     <t>connection</t>
   </si>
   <si>
-    <t>Jio</t>
-  </si>
-  <si>
     <t>SKA</t>
   </si>
   <si>
@@ -57,55 +54,19 @@
     <t>Digicredit</t>
   </si>
   <si>
-    <t>9984125538</t>
-  </si>
-  <si>
-    <t>24-07-2026</t>
-  </si>
-  <si>
     <t>Rcom</t>
   </si>
   <si>
-    <t>9735816783</t>
-  </si>
-  <si>
-    <t>26-07-2026</t>
-  </si>
-  <si>
-    <t>Shree Balaji associate</t>
-  </si>
-  <si>
-    <t>Cryptomonk</t>
-  </si>
-  <si>
-    <t>Nextgen services</t>
-  </si>
-  <si>
-    <t>PursuitCX</t>
-  </si>
-  <si>
-    <t>salary on time</t>
-  </si>
-  <si>
-    <t>Stefto</t>
-  </si>
-  <si>
-    <t>8860812829</t>
-  </si>
-  <si>
     <t>stefto</t>
   </si>
   <si>
-    <t>Mahavir</t>
-  </si>
-  <si>
-    <t>7905301218</t>
-  </si>
-  <si>
-    <t>Strideone</t>
-  </si>
-  <si>
-    <t>VGM</t>
+    <t>Vi</t>
+  </si>
+  <si>
+    <t>Allset</t>
+  </si>
+  <si>
+    <t>cryptomonk</t>
   </si>
 </sst>
 </file>
@@ -115,7 +76,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy\ hh:mm"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,12 +96,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -186,20 +141,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -209,24 +152,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BBAE93-43D1-46F0-9E47-865BBF288536}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
@@ -549,447 +487,127 @@
     <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="7"/>
+    <col min="6" max="6" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>7</v>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>8213846319</v>
-      </c>
-      <c r="B2" s="1">
-        <v>8074615582</v>
-      </c>
-      <c r="C2" s="12">
-        <v>46225.469444444447</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
+      <c r="A2" s="2">
+        <v>8917117134</v>
+      </c>
+      <c r="B2" s="2">
+        <v>8789154762</v>
+      </c>
+      <c r="C2" s="5">
+        <v>46239</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>8213847431</v>
-      </c>
-      <c r="B3" s="1">
-        <v>9676654721</v>
-      </c>
-      <c r="C3" s="13">
-        <v>46237.211111111108</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
+      <c r="A3" s="2">
+        <v>8917116999</v>
+      </c>
+      <c r="B3" s="2">
+        <v>7824950479</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46238</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>8213847518</v>
-      </c>
-      <c r="B4" s="1">
-        <v>9527314872</v>
-      </c>
-      <c r="C4" s="13">
-        <v>46237.304166666669</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="A4" s="6">
+        <v>8213847455</v>
+      </c>
+      <c r="B4" s="6">
+        <v>9553905626</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46239.506249999999</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>8213827736</v>
-      </c>
-      <c r="B5" s="1">
-        <v>9939363385</v>
-      </c>
-      <c r="C5" s="12">
-        <v>46224.552777777775</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="A5" s="6">
+        <v>8213846423</v>
+      </c>
+      <c r="B5" s="6">
+        <v>8973937536</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46240.267361111109</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6">
+      <c r="E5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>8213847240</v>
-      </c>
-      <c r="B6" s="1">
-        <v>7988340945</v>
-      </c>
-      <c r="C6" s="12">
-        <v>46226.493055555555</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="A6" s="6">
+        <v>8213846317</v>
+      </c>
+      <c r="B6" s="6">
+        <v>9866045199</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46240.272222222222</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>8213847240</v>
-      </c>
-      <c r="B7" s="1">
-        <v>9990930001</v>
-      </c>
-      <c r="C7" s="12">
-        <v>46226.497916666667</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>8213846807</v>
-      </c>
-      <c r="B8" s="1">
-        <v>9966102667</v>
-      </c>
-      <c r="C8" s="13">
-        <v>46219.770833333336</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>8213847464</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7993637639</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46226.930555555555</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>8213847426</v>
-      </c>
-      <c r="B10" s="1">
-        <v>9686505209</v>
-      </c>
-      <c r="C10" s="13">
-        <v>46237.184027777781</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>8213846738</v>
-      </c>
-      <c r="B11" s="1">
-        <v>7905301218</v>
-      </c>
-      <c r="C11" s="13">
-        <v>46238.200694444444</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>8213847131</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8860812829</v>
-      </c>
-      <c r="C12" s="13">
-        <v>46234.29791666667</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>8213846728</v>
-      </c>
-      <c r="B13" s="1">
-        <v>9771436278</v>
-      </c>
-      <c r="C13" s="13">
-        <v>46234.495833333334</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>8213846727</v>
-      </c>
-      <c r="B14" s="1">
-        <v>9952466520</v>
-      </c>
-      <c r="C14" s="13">
-        <v>46236.770833333336</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>8213846736</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="13">
-        <v>46235.3125</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>8213847131</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="13">
-        <v>46235.183333333334</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>8213842180</v>
-      </c>
-      <c r="B17" s="1">
-        <v>9995866686</v>
-      </c>
-      <c r="C17" s="13">
-        <v>46234.201388888891</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
-        <v>8645426989</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
-        <v>8645426990</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
-        <v>8913117722</v>
-      </c>
-      <c r="B20" s="3">
-        <v>9118409892</v>
-      </c>
-      <c r="C20" s="4">
-        <v>46231</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
-        <v>8645426215</v>
-      </c>
-      <c r="B21" s="3">
-        <v>9735816783</v>
-      </c>
-      <c r="C21" s="4">
-        <v>46231</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="8">
-        <v>8645426217</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
